--- a/Codes_2025/Trial 3/Trial3_LR_Leaders_Results.xlsx
+++ b/Codes_2025/Trial 3/Trial3_LR_Leaders_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,10 +473,10 @@
         <v>22.34</v>
       </c>
       <c r="D2" t="n">
-        <v>17.04292935851546</v>
+        <v>21.99960858592566</v>
       </c>
       <c r="E2" t="n">
-        <v>5.297070641484538</v>
+        <v>0.340391414074336</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -497,10 +497,10 @@
         <v>35.4</v>
       </c>
       <c r="D3" t="n">
-        <v>20.05510670509874</v>
+        <v>24.25153178697469</v>
       </c>
       <c r="E3" t="n">
-        <v>15.34489329490125</v>
+        <v>11.14846821302531</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -521,10 +521,10 @@
         <v>6.549999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>19.4274161117555</v>
+        <v>23.18490026054841</v>
       </c>
       <c r="E4" t="n">
-        <v>12.8774161117555</v>
+        <v>16.63490026054841</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -545,10 +545,10 @@
         <v>69.53000000000007</v>
       </c>
       <c r="D5" t="n">
-        <v>21.26401802314512</v>
+        <v>24.60823704141917</v>
       </c>
       <c r="E5" t="n">
-        <v>48.26598197685495</v>
+        <v>44.9217629585809</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -559,20 +559,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>21.01</v>
+        <v>37.81</v>
       </c>
       <c r="D6" t="n">
-        <v>24.42584210210585</v>
+        <v>18.56467728917808</v>
       </c>
       <c r="E6" t="n">
-        <v>3.415842102105845</v>
+        <v>19.24532271082192</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -583,20 +583,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>20.08</v>
+        <v>21.01</v>
       </c>
       <c r="D7" t="n">
-        <v>27.98982185284466</v>
+        <v>26.87528791466749</v>
       </c>
       <c r="E7" t="n">
-        <v>7.909821852844658</v>
+        <v>5.865287914667487</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -607,20 +607,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>9.359999999999999</v>
+        <v>20.08</v>
       </c>
       <c r="D8" t="n">
-        <v>25.80800482070328</v>
+        <v>29.29870341194683</v>
       </c>
       <c r="E8" t="n">
-        <v>16.44800482070328</v>
+        <v>9.21870341194683</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -631,20 +631,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>7.180000000000001</v>
+        <v>6.81</v>
       </c>
       <c r="D9" t="n">
-        <v>19.74598874182423</v>
+        <v>19.0962428051789</v>
       </c>
       <c r="E9" t="n">
-        <v>12.56598874182423</v>
+        <v>12.2862428051789</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -655,20 +655,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>37.67999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>22.10916893075982</v>
+        <v>26.91033102844621</v>
       </c>
       <c r="E10" t="n">
-        <v>15.57083106924017</v>
+        <v>17.55033102844621</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -679,20 +679,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>7.73</v>
+        <v>7.180000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>15.0583626289423</v>
+        <v>23.24358349877166</v>
       </c>
       <c r="E11" t="n">
-        <v>7.3283626289423</v>
+        <v>16.06358349877166</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -703,20 +703,20 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>6.590000000000001</v>
+        <v>37.67999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>14.15810710792367</v>
+        <v>25.07368052900495</v>
       </c>
       <c r="E12" t="n">
-        <v>7.568107107923665</v>
+        <v>12.60631947099504</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -727,20 +727,20 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2025</v>
       </c>
       <c r="C13" t="n">
-        <v>10.19</v>
+        <v>7.73</v>
       </c>
       <c r="D13" t="n">
-        <v>17.72709910778838</v>
+        <v>18.60071511395172</v>
       </c>
       <c r="E13" t="n">
-        <v>7.537099107788379</v>
+        <v>10.87071511395172</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -751,22 +751,94 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C14" t="n">
+        <v>24.26000000000001</v>
+      </c>
+      <c r="D14" t="n">
+        <v>19.52490274808321</v>
+      </c>
+      <c r="E14" t="n">
+        <v>4.735097251916798</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C15" t="n">
+        <v>6.590000000000001</v>
+      </c>
+      <c r="D15" t="n">
+        <v>18.73540503354118</v>
+      </c>
+      <c r="E15" t="n">
+        <v>12.14540503354118</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C16" t="n">
+        <v>10.19</v>
+      </c>
+      <c r="D16" t="n">
+        <v>21.5167680243067</v>
+      </c>
+      <c r="E16" t="n">
+        <v>11.3267680243067</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Leaders</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>Sweden</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C14" t="n">
+      <c r="B17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C17" t="n">
         <v>37.58000000000002</v>
       </c>
-      <c r="D14" t="n">
-        <v>25.33325261115951</v>
-      </c>
-      <c r="E14" t="n">
-        <v>12.24674738884051</v>
-      </c>
-      <c r="F14" t="inlineStr">
+      <c r="D17" t="n">
+        <v>27.82879966400734</v>
+      </c>
+      <c r="E17" t="n">
+        <v>9.751200335992682</v>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Leaders</t>
         </is>
